--- a/db/seed/seed_Instance_table.xlsx
+++ b/db/seed/seed_Instance_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skeye\BOOK2\MAKEDOC\db\seed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF242771-D9E8-48BE-8027-19D308B310FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842A1C3C-22F3-429A-A87C-7B6A083DF98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5F0BAD6A-9439-4F6A-BF23-1D648A48E164}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>InstanceID</t>
   </si>
@@ -90,9 +90,6 @@
   </si>
   <si>
     <t>Title</t>
-  </si>
-  <si>
-    <t>OutputFile</t>
   </si>
   <si>
     <t>5515e87f</t>
@@ -483,17 +480,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75CD4F2A-358E-4749-8E6C-47000687AB01}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.33203125" customWidth="1"/>
     <col min="2" max="7" width="12.77734375" customWidth="1"/>
     <col min="8" max="8" width="21.21875" customWidth="1"/>
-    <col min="9" max="11" width="12.77734375" customWidth="1"/>
-    <col min="12" max="13" width="20.77734375" customWidth="1"/>
+    <col min="9" max="10" width="12.77734375" customWidth="1"/>
+    <col min="11" max="12" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -519,84 +516,81 @@
         <v>16</v>
       </c>
       <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>17</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>18</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1">
         <f ca="1">TODAY()</f>
-        <v>46150</v>
+        <v>46169</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1">
         <f t="shared" ref="E3:E4" ca="1" si="0">TODAY()</f>
-        <v>46150</v>
+        <v>46169</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>46150</v>
+        <v>46169</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" t="s">
         <v>15</v>
       </c>
     </row>
